--- a/diplom/excel/график_3_capex.xlsx
+++ b/diplom/excel/график_3_capex.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -56,7 +60,7 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +188,9 @@
           </val>
         </ser>
         <dLbls>
+          <showVal val="0"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
           <showPercent val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
@@ -517,7 +524,7 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -546,7 +553,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Климатическая камера</t>
+          <t>Климат. камера</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -556,7 +563,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Пресс-форма корпуса</t>
+          <t>Пресс-форма</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -576,7 +583,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Антистатическая мебель</t>
+          <t>Антистат. мебель</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -596,7 +603,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Сертификация ТР ЕАЭС</t>
+          <t>Сертификация</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -606,7 +613,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Прочее оборудование</t>
+          <t>Прочее оборуд.</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -616,7 +623,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Прочее (госпошлина, реклама, и т.д.)</t>
+          <t>Прочее (пошлины и т.д.)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">

--- a/diplom/excel/график_3_capex.xlsx
+++ b/diplom/excel/график_3_capex.xlsx
@@ -30,6 +30,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -42,7 +43,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,6 +145,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="26"/>
   <chart>
     <title>
       <tx>
@@ -154,14 +156,14 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Структура капитальных вложений проекта (CAPEX)</a:t>
+              <a:t>Структура капитальных вложений (CAPEX)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <pieChart>
+      <doughnutChart>
         <varyColors val="1"/>
         <ser>
           <idx val="0"/>
@@ -194,7 +196,8 @@
           <showPercent val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
-      </pieChart>
+        <holeSize val="10"/>
+      </doughnutChart>
     </plotArea>
     <legend>
       <legendPos val="r"/>
@@ -524,7 +527,7 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -573,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ремонт ESD-зоны</t>
+          <t>Ремонт ESD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -623,7 +626,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Прочее (пошлины и т.д.)</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
